--- a/file/table4.xlsx
+++ b/file/table4.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,8 +127,8 @@
   </si>
   <si>
     <t>设防水位：8.5
-警戒水位：9.5
-保证水位：11.5</t>
+警戒水位：10.5
+保证水位：12.65</t>
   </si>
   <si>
     <t>惠生连圩堤：
@@ -613,6 +613,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -642,19 +655,6 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -917,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -943,40 +943,50 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -987,13 +997,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1315,13 +1318,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.75454545454545" customWidth="1"/>
+    <col min="1" max="1" width="3.75833333333333" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="15.6272727272727" customWidth="1"/>
-    <col min="4" max="7" width="11.8727272727273" customWidth="1"/>
-    <col min="8" max="9" width="11.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="7" width="11.875" customWidth="1"/>
+    <col min="8" max="9" width="11.2583333333333" customWidth="1"/>
     <col min="10" max="16383" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1338,7 +1341,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" customFormat="1" ht="14.25" customHeight="1" spans="1:1">
+    <row r="2" customFormat="1" ht="14.25" customHeight="1" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1368,22 +1371,22 @@
       <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="20" customHeight="1" spans="1:9">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
@@ -1394,260 +1397,260 @@
       </c>
     </row>
     <row r="5" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15">
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16">
         <f t="shared" ref="F5:F14" si="0">D5-E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17">
+      <c r="G5" s="17"/>
+      <c r="H5" s="18">
         <v>44025</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="19">
         <v>15.21</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A6" s="18">
+      <c r="A6" s="20">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15">
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17">
+      <c r="G6" s="17"/>
+      <c r="H6" s="18">
         <v>44033</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="19">
         <v>12.76</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A7" s="18">
+      <c r="A7" s="20">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15">
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17">
+      <c r="G7" s="17"/>
+      <c r="H7" s="18">
         <v>44033</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="23">
         <v>12.72</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A8" s="18">
+      <c r="A8" s="20">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17">
+      <c r="G8" s="17"/>
+      <c r="H8" s="18">
         <v>44029</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="19">
         <v>13.19</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A9" s="18">
+      <c r="A9" s="20">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17">
+      <c r="G9" s="17"/>
+      <c r="H9" s="18">
         <v>44033</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="23">
         <v>12.72</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A10" s="18">
+      <c r="A10" s="20">
         <v>6</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15">
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17">
+      <c r="G10" s="17"/>
+      <c r="H10" s="18">
         <v>44033</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="23">
         <v>12.77</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A11" s="18">
+      <c r="A11" s="20">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17">
+      <c r="G11" s="17"/>
+      <c r="H11" s="18">
         <v>44030</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="23">
         <v>12.1</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A12" s="18">
+      <c r="A12" s="20">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15">
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17">
+      <c r="G12" s="17"/>
+      <c r="H12" s="18">
         <v>44025</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="23">
         <v>15.21</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A13" s="18">
+      <c r="A13" s="20">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17">
+      <c r="G13" s="17"/>
+      <c r="H13" s="18">
         <v>44025</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="23">
         <v>15.21</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="38.25" customHeight="1" spans="1:9">
-      <c r="A14" s="21">
+      <c r="A14" s="25">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17">
+      <c r="G14" s="17"/>
+      <c r="H14" s="18">
         <v>44025</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="23">
         <v>15.21</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
     </row>
-    <row r="16" customFormat="1" spans="1:1">
-      <c r="A16" s="23" t="s">
+    <row r="16" customFormat="1" spans="1:9">
+      <c r="A16" s="27" t="s">
         <v>33</v>
       </c>
     </row>
